--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
@@ -3252,7 +3252,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T03:54:20.708Z</t>
+    <t>2026-10-02T04:13:59.531Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
@@ -3252,7 +3252,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T04:13:59.531Z</t>
+    <t>2026-10-02T15:08:52.150Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
@@ -3252,7 +3252,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T15:08:52.150Z</t>
+    <t>2026-10-02T15:30:07.067Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
@@ -3252,7 +3252,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T15:30:07.067Z</t>
+    <t>2026-10-02T16:18:52.116Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
@@ -3252,7 +3252,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T16:18:52.116Z</t>
+    <t>2026-10-02T19:28:14.434Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
@@ -3252,7 +3252,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T19:28:14.434Z</t>
+    <t>2026-10-02T19:44:35.290Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
@@ -2034,7 +2034,7 @@
     <t>expiresAt - createdAt = 30 min; timeout behaviour shown; no reservation exists</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml, REQ-122, BR-122</t>
+    <t>AQPI-15, REQ-122, BR-122</t>
   </si>
   <si>
     <t>TC-F-113</t>
@@ -2060,7 +2060,7 @@
     <t>Revalidation requires acknowledgement; first submit HTTP 409 PRICE_CHANGE_REQUIRES_ACKNOWLEDGEMENT; after acknowledging HTTP 201</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml, REQ-123, BR-123</t>
+    <t>AQPI-17, REQ-123, BR-123</t>
   </si>
   <si>
     <t>TC-F-114</t>
@@ -2099,7 +2099,7 @@
     <t>First 3 resends HTTP 202, the next HTTP 429; still one reservation</t>
   </si>
   <si>
-    <t>notification-service/src/main/resources/notification-service.yml, REQ-124, BR-124</t>
+    <t>AQPI-26, REQ-124, BR-124</t>
   </si>
   <si>
     <t>TC-F-116</t>
@@ -2118,7 +2118,7 @@
     <t>HTTP 400 IDEMPOTENCY_KEY_REQUIRED</t>
   </si>
   <si>
-    <t>reservation-service/src/main/resources/reservation-service.yml, REQ-125, BR-125</t>
+    <t>AQPI-21, REQ-125, BR-125</t>
   </si>
   <si>
     <t>TC-F-117</t>
@@ -2168,7 +2168,7 @@
     <t>HTTP 200 with a searchId</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-126, BR-126</t>
+    <t>AQPI-4, REQ-126, BR-126</t>
   </si>
   <si>
     <t>TC-F-120</t>
@@ -2234,7 +2234,7 @@
     <t>occupancy.adults=4; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-127, BR-127</t>
+    <t>AQPI-4, REQ-127, BR-127</t>
   </si>
   <si>
     <t>TC-F-124</t>
@@ -2306,7 +2306,7 @@
     <t>stay.checkInOffsetDays=500; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-128, BR-128</t>
+    <t>AQPI-4, REQ-128, BR-128</t>
   </si>
   <si>
     <t>TC-F-128</t>
@@ -3252,7 +3252,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T19:44:35.290Z</t>
+    <t>2026-10-02T20:05:33.940Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
@@ -3252,7 +3252,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T20:05:33.940Z</t>
+    <t>2026-10-02T20:26:37.517Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-1/04-test-cases/CYC-1-test-cases.xlsx
@@ -3252,7 +3252,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T20:26:37.517Z</t>
+    <t>2026-10-02T20:29:20.215Z</t>
   </si>
   <si>
     <t>Column order</t>
